--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -460,72 +460,72 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.1838</v>
+        <v>16.80529</v>
       </c>
       <c r="D2" t="n">
-        <v>16.82553</v>
+        <v>16.6033</v>
       </c>
       <c r="E2" t="n">
-        <v>17.01209</v>
+        <v>16.75114</v>
       </c>
       <c r="F2" t="n">
-        <v>43.19647</v>
+        <v>42.87647</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05032</v>
+        <v>0.05133</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82691</v>
+        <v>1.82716</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.94095</v>
+        <v>17.12967</v>
       </c>
       <c r="D3" t="n">
-        <v>16.97506</v>
+        <v>16.51786</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70897</v>
+        <v>16.75025</v>
       </c>
       <c r="F3" t="n">
-        <v>42.57057</v>
+        <v>42.26372</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05124</v>
+        <v>0.05162</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82566</v>
+        <v>1.83374</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.91681</v>
+        <v>17.27042</v>
       </c>
       <c r="D4" t="n">
-        <v>16.85716</v>
+        <v>16.53674</v>
       </c>
       <c r="E4" t="n">
-        <v>16.83118</v>
+        <v>16.77869</v>
       </c>
       <c r="F4" t="n">
-        <v>42.57782</v>
+        <v>42.93972</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05171</v>
+        <v>0.04941</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81873</v>
+        <v>1.83233</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.93013</v>
+        <v>17.03299</v>
       </c>
       <c r="D5" t="n">
-        <v>16.61325</v>
+        <v>16.55033</v>
       </c>
       <c r="E5" t="n">
-        <v>16.64421</v>
+        <v>16.62135</v>
       </c>
       <c r="F5" t="n">
-        <v>41.97654</v>
+        <v>42.85277</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04956</v>
+        <v>0.0492</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84646</v>
+        <v>1.78374</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.09567</v>
+        <v>16.82958</v>
       </c>
       <c r="D6" t="n">
-        <v>16.69107</v>
+        <v>16.7286</v>
       </c>
       <c r="E6" t="n">
-        <v>17.05664</v>
+        <v>16.73284</v>
       </c>
       <c r="F6" t="n">
-        <v>42.44626</v>
+        <v>43.13051</v>
       </c>
       <c r="G6" t="n">
         <v>0.05072</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8629</v>
+        <v>1.78462</v>
       </c>
     </row>
     <row r="7">
@@ -585,1922 +585,1611 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.66708</v>
+        <v>16.97221</v>
       </c>
       <c r="D7" t="n">
-        <v>16.5913</v>
+        <v>16.45066</v>
       </c>
       <c r="E7" t="n">
-        <v>16.638</v>
+        <v>16.73672</v>
       </c>
       <c r="F7" t="n">
-        <v>42.01902</v>
+        <v>43.24488</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05113</v>
+        <v>0.05112</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83473</v>
+        <v>1.81756</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.12564</v>
+        <v>17.10453</v>
       </c>
       <c r="D8" t="n">
-        <v>16.38074</v>
+        <v>16.82725</v>
       </c>
       <c r="E8" t="n">
-        <v>16.85732</v>
+        <v>16.97289</v>
       </c>
       <c r="F8" t="n">
-        <v>42.08448</v>
+        <v>43.42153</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05151</v>
+        <v>0.0506</v>
       </c>
       <c r="H8" t="n">
-        <v>1.87173</v>
+        <v>1.86728</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.84488</v>
+        <v>17.11404</v>
       </c>
       <c r="D9" t="n">
-        <v>17.06535</v>
+        <v>16.67357</v>
       </c>
       <c r="E9" t="n">
-        <v>16.54284</v>
+        <v>16.88421</v>
       </c>
       <c r="F9" t="n">
-        <v>42.52678</v>
+        <v>41.96902</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05097</v>
+        <v>0.05056</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84893</v>
+        <v>1.83889</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.99817</v>
+        <v>16.83731</v>
       </c>
       <c r="D10" t="n">
-        <v>16.62817</v>
+        <v>16.54001</v>
       </c>
       <c r="E10" t="n">
-        <v>16.59098</v>
+        <v>16.60637</v>
       </c>
       <c r="F10" t="n">
-        <v>42.81308</v>
+        <v>42.56842</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05067</v>
+        <v>0.0505</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83983</v>
+        <v>1.84283</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 10</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.96609</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.52866</v>
-      </c>
-      <c r="E11" t="n">
-        <v>17.06152</v>
-      </c>
-      <c r="F11" t="n">
-        <v>43.24925</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05094</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.84825</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 11</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.29635</v>
+        <v>16.71062</v>
       </c>
       <c r="D12" t="n">
-        <v>16.71604</v>
+        <v>16.47654</v>
       </c>
       <c r="E12" t="n">
-        <v>16.74588</v>
+        <v>16.56295</v>
       </c>
       <c r="F12" t="n">
-        <v>42.58563</v>
+        <v>42.72831</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05046</v>
+        <v>0.05226</v>
       </c>
       <c r="H12" t="n">
-        <v>1.85192</v>
+        <v>1.84712</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 12</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.86097</v>
+        <v>17.04713</v>
       </c>
       <c r="D13" t="n">
-        <v>16.44651</v>
+        <v>16.50426</v>
       </c>
       <c r="E13" t="n">
-        <v>16.83062</v>
+        <v>17.01052</v>
       </c>
       <c r="F13" t="n">
-        <v>43.37571</v>
+        <v>41.63022</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05116</v>
+        <v>0.05149</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8521</v>
+        <v>1.84201</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 13</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.03276</v>
+        <v>17.20438</v>
       </c>
       <c r="D14" t="n">
-        <v>16.86095</v>
+        <v>16.66165</v>
       </c>
       <c r="E14" t="n">
-        <v>16.5354</v>
+        <v>16.7612</v>
       </c>
       <c r="F14" t="n">
-        <v>42.57559</v>
+        <v>42.20659</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05082</v>
+        <v>0.05055</v>
       </c>
       <c r="H14" t="n">
-        <v>1.86178</v>
+        <v>1.83395</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 14</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.86564</v>
+        <v>16.77484</v>
       </c>
       <c r="D15" t="n">
-        <v>16.60103</v>
+        <v>16.71091</v>
       </c>
       <c r="E15" t="n">
-        <v>16.96889</v>
+        <v>16.72365</v>
       </c>
       <c r="F15" t="n">
-        <v>42.87232</v>
+        <v>42.09422</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05024</v>
+        <v>0.05127</v>
       </c>
       <c r="H15" t="n">
-        <v>1.83796</v>
+        <v>1.83726</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 15</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.78313</v>
+        <v>16.83443</v>
       </c>
       <c r="D16" t="n">
-        <v>16.63025</v>
+        <v>16.63092</v>
       </c>
       <c r="E16" t="n">
-        <v>16.49727</v>
+        <v>16.64667</v>
       </c>
       <c r="F16" t="n">
-        <v>42.48338</v>
+        <v>42.79102</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0512</v>
+        <v>0.05076</v>
       </c>
       <c r="H16" t="n">
-        <v>1.81711</v>
+        <v>1.8427</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 16</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.02357</v>
+        <v>17.00851</v>
       </c>
       <c r="D17" t="n">
-        <v>16.70938</v>
+        <v>16.82905</v>
       </c>
       <c r="E17" t="n">
-        <v>16.81944</v>
+        <v>16.87761</v>
       </c>
       <c r="F17" t="n">
-        <v>42.94313</v>
+        <v>42.44825</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05149</v>
+        <v>0.05125</v>
       </c>
       <c r="H17" t="n">
-        <v>1.81273</v>
+        <v>1.79011</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 17</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.00219</v>
+        <v>16.84682</v>
       </c>
       <c r="D18" t="n">
-        <v>16.93886</v>
+        <v>16.55919</v>
       </c>
       <c r="E18" t="n">
-        <v>16.77007</v>
+        <v>16.75719</v>
       </c>
       <c r="F18" t="n">
-        <v>42.84392</v>
+        <v>42.40004</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05128</v>
+        <v>0.05111</v>
       </c>
       <c r="H18" t="n">
-        <v>1.81207</v>
+        <v>1.84882</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 18</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.21398</v>
+        <v>17.14703</v>
       </c>
       <c r="D19" t="n">
-        <v>16.77292</v>
+        <v>16.82437</v>
       </c>
       <c r="E19" t="n">
-        <v>17.12816</v>
+        <v>16.99896</v>
       </c>
       <c r="F19" t="n">
-        <v>42.76621</v>
+        <v>43.79615</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05115</v>
+        <v>0.05117</v>
       </c>
       <c r="H19" t="n">
-        <v>1.80361</v>
+        <v>1.81603</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 19</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.86839</v>
+        <v>17.44851</v>
       </c>
       <c r="D20" t="n">
-        <v>16.96541</v>
+        <v>16.56937</v>
       </c>
       <c r="E20" t="n">
-        <v>16.91518</v>
+        <v>16.66218</v>
       </c>
       <c r="F20" t="n">
-        <v>43.46443</v>
+        <v>43.12816</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05019</v>
+        <v>0.05116</v>
       </c>
       <c r="H20" t="n">
-        <v>1.83935</v>
+        <v>1.80935</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 20</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>16.91499</v>
-      </c>
-      <c r="D21" t="n">
-        <v>16.71212</v>
-      </c>
-      <c r="E21" t="n">
-        <v>16.69231</v>
-      </c>
-      <c r="F21" t="n">
-        <v>43.25929</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.05046</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.84782</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 21</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.01441</v>
+        <v>15.92481</v>
       </c>
       <c r="D22" t="n">
-        <v>16.70828</v>
+        <v>15.70134</v>
       </c>
       <c r="E22" t="n">
-        <v>16.73958</v>
+        <v>15.78324</v>
       </c>
       <c r="F22" t="n">
-        <v>43.89527</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05123</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.84728</v>
+        <v>250.08477</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 22</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.81606</v>
+        <v>15.95967</v>
       </c>
       <c r="D23" t="n">
-        <v>16.78651</v>
+        <v>15.68936</v>
       </c>
       <c r="E23" t="n">
-        <v>17.11861</v>
+        <v>15.83878</v>
       </c>
       <c r="F23" t="n">
-        <v>42.02802</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05035</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.80417</v>
+        <v>256.61895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 23</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.90267</v>
+        <v>15.9706</v>
       </c>
       <c r="D24" t="n">
-        <v>16.5054</v>
+        <v>15.55578</v>
       </c>
       <c r="E24" t="n">
-        <v>16.85599</v>
+        <v>15.84842</v>
       </c>
       <c r="F24" t="n">
-        <v>42.36796</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.05052</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.83141</v>
+        <v>252.54735</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 24</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.99179</v>
+        <v>16.08449</v>
       </c>
       <c r="D25" t="n">
-        <v>16.7512</v>
+        <v>15.60911</v>
       </c>
       <c r="E25" t="n">
-        <v>16.81582</v>
+        <v>15.65346</v>
       </c>
       <c r="F25" t="n">
-        <v>42.58931</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.05049</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.84109</v>
+        <v>257.41705</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 25</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.74066</v>
+        <v>16.13316</v>
       </c>
       <c r="D26" t="n">
-        <v>16.86898</v>
+        <v>15.70767</v>
       </c>
       <c r="E26" t="n">
-        <v>16.81236</v>
+        <v>16.02172</v>
       </c>
       <c r="F26" t="n">
-        <v>41.92472</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.05182</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.86005</v>
+        <v>257.36738</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 26</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.71347</v>
+        <v>15.88178</v>
       </c>
       <c r="D27" t="n">
-        <v>16.63902</v>
+        <v>15.73264</v>
       </c>
       <c r="E27" t="n">
-        <v>16.75799</v>
+        <v>15.86515</v>
       </c>
       <c r="F27" t="n">
-        <v>42.38241</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.05124</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.81127</v>
+        <v>257.92732</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 27</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.94641</v>
+        <v>15.96043</v>
       </c>
       <c r="D28" t="n">
-        <v>16.83696</v>
+        <v>15.63969</v>
       </c>
       <c r="E28" t="n">
-        <v>16.74894</v>
+        <v>15.82433</v>
       </c>
       <c r="F28" t="n">
-        <v>42.38014</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.05036</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.86869</v>
+        <v>255.1735</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 28</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16.70423</v>
+        <v>15.77297</v>
       </c>
       <c r="D29" t="n">
-        <v>16.92997</v>
+        <v>15.4028</v>
       </c>
       <c r="E29" t="n">
-        <v>16.80932</v>
+        <v>15.67138</v>
       </c>
       <c r="F29" t="n">
-        <v>43.69625</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.05115</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.80401</v>
+        <v>256.96652</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Unit 29</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.97141</v>
+        <v>15.89437</v>
       </c>
       <c r="D30" t="n">
-        <v>16.20541</v>
+        <v>15.60232</v>
       </c>
       <c r="E30" t="n">
-        <v>16.79635</v>
+        <v>15.70118</v>
       </c>
       <c r="F30" t="n">
-        <v>41.87432</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05193</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.81324</v>
+        <v>252.4258</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Unit 30</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>16.93705</v>
-      </c>
-      <c r="D31" t="n">
-        <v>16.13648</v>
-      </c>
-      <c r="E31" t="n">
-        <v>16.35097</v>
-      </c>
-      <c r="F31" t="n">
-        <v>42.32536</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.05101</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.83595</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unit 31</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17.04682</v>
+        <v>16.85421</v>
       </c>
       <c r="D32" t="n">
-        <v>16.63467</v>
+        <v>16.22175</v>
       </c>
       <c r="E32" t="n">
-        <v>16.35906</v>
+        <v>16.62862</v>
       </c>
       <c r="F32" t="n">
-        <v>42.94174</v>
+        <v>21.77102</v>
       </c>
       <c r="G32" t="n">
-        <v>0.05103</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.79462</v>
+        <v>34.99372</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unit 32</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17.09202</v>
+        <v>16.85449</v>
       </c>
       <c r="D33" t="n">
-        <v>16.76659</v>
+        <v>15.83412</v>
       </c>
       <c r="E33" t="n">
-        <v>16.66095</v>
+        <v>16.41149</v>
       </c>
       <c r="F33" t="n">
-        <v>43.27651</v>
+        <v>22.0993</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0513</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.85159</v>
+        <v>34.7269</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unit 33</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17.16184</v>
+        <v>16.45293</v>
       </c>
       <c r="D34" t="n">
-        <v>16.59547</v>
+        <v>16.33596</v>
       </c>
       <c r="E34" t="n">
-        <v>17.1167</v>
+        <v>16.39199</v>
       </c>
       <c r="F34" t="n">
-        <v>43.30059</v>
+        <v>22.21173</v>
       </c>
       <c r="G34" t="n">
-        <v>0.05083</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.84191</v>
+        <v>34.7273</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unit 34</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.58776</v>
+        <v>17.022</v>
       </c>
       <c r="D35" t="n">
-        <v>16.58455</v>
+        <v>16.05029</v>
       </c>
       <c r="E35" t="n">
-        <v>16.85653</v>
+        <v>16.84326</v>
       </c>
       <c r="F35" t="n">
-        <v>42.60041</v>
+        <v>21.77665</v>
       </c>
       <c r="G35" t="n">
-        <v>0.05043</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.8116</v>
+        <v>34.96918</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unit 35</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.82466</v>
+        <v>17.00566</v>
       </c>
       <c r="D36" t="n">
-        <v>16.56517</v>
+        <v>16.25475</v>
       </c>
       <c r="E36" t="n">
-        <v>16.89265</v>
+        <v>16.78352</v>
       </c>
       <c r="F36" t="n">
-        <v>41.68763</v>
+        <v>22.02225</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0505</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.82298</v>
+        <v>34.10006</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unit 36</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.88786</v>
+        <v>16.67863</v>
       </c>
       <c r="D37" t="n">
-        <v>17.14102</v>
+        <v>15.82772</v>
       </c>
       <c r="E37" t="n">
-        <v>16.93191</v>
+        <v>16.57265</v>
       </c>
       <c r="F37" t="n">
-        <v>43.03866</v>
+        <v>21.41378</v>
       </c>
       <c r="G37" t="n">
-        <v>0.05032</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.85969</v>
+        <v>34.62969</v>
       </c>
     </row>
     <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.5478</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.33554</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.47636</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22.00358</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.63104</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.35473</v>
+        <v>16.66205</v>
       </c>
       <c r="D39" t="n">
-        <v>16.27092</v>
+        <v>16.03169</v>
       </c>
       <c r="E39" t="n">
-        <v>16.57808</v>
+        <v>16.33414</v>
       </c>
       <c r="F39" t="n">
-        <v>21.70878</v>
+        <v>21.94476</v>
       </c>
       <c r="G39" t="n">
-        <v>34.33926</v>
+        <v>34.43433</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.20438</v>
+        <v>16.98217</v>
       </c>
       <c r="D40" t="n">
-        <v>15.87772</v>
+        <v>16.24725</v>
       </c>
       <c r="E40" t="n">
-        <v>16.37682</v>
+        <v>16.5104</v>
       </c>
       <c r="F40" t="n">
-        <v>21.90547</v>
+        <v>22.18844</v>
       </c>
       <c r="G40" t="n">
-        <v>34.02584</v>
+        <v>34.18819</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>16.87713</v>
-      </c>
-      <c r="D41" t="n">
-        <v>16.01416</v>
-      </c>
-      <c r="E41" t="n">
-        <v>16.23634</v>
-      </c>
-      <c r="F41" t="n">
-        <v>22.04786</v>
-      </c>
-      <c r="G41" t="n">
-        <v>34.4997</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16.53073</v>
+        <v>17.08896</v>
       </c>
       <c r="D42" t="n">
-        <v>16.03764</v>
+        <v>15.88455</v>
       </c>
       <c r="E42" t="n">
-        <v>16.52835</v>
+        <v>16.15521</v>
       </c>
       <c r="F42" t="n">
-        <v>21.90493</v>
+        <v>21.70131</v>
       </c>
       <c r="G42" t="n">
-        <v>34.31462</v>
+        <v>33.99035</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.89138</v>
+        <v>16.83089</v>
       </c>
       <c r="D43" t="n">
-        <v>16.06423</v>
+        <v>16.17058</v>
       </c>
       <c r="E43" t="n">
-        <v>16.80109</v>
+        <v>16.67872</v>
       </c>
       <c r="F43" t="n">
-        <v>21.92876</v>
+        <v>21.81357</v>
       </c>
       <c r="G43" t="n">
-        <v>34.16073</v>
+        <v>34.97847</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16.91186</v>
+        <v>16.55389</v>
       </c>
       <c r="D44" t="n">
-        <v>15.71321</v>
+        <v>16.21227</v>
       </c>
       <c r="E44" t="n">
-        <v>16.35341</v>
+        <v>16.47085</v>
       </c>
       <c r="F44" t="n">
-        <v>21.70869</v>
+        <v>21.92435</v>
       </c>
       <c r="G44" t="n">
-        <v>34.51045</v>
+        <v>34.01586</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.65716</v>
+        <v>16.46142</v>
       </c>
       <c r="D45" t="n">
-        <v>16.14961</v>
+        <v>15.79601</v>
       </c>
       <c r="E45" t="n">
-        <v>16.63936</v>
+        <v>16.38254</v>
       </c>
       <c r="F45" t="n">
-        <v>22.20851</v>
+        <v>21.71489</v>
       </c>
       <c r="G45" t="n">
-        <v>34.67461</v>
+        <v>34.07072</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.99896</v>
+        <v>16.80342</v>
       </c>
       <c r="D46" t="n">
-        <v>16.4757</v>
+        <v>15.79574</v>
       </c>
       <c r="E46" t="n">
-        <v>16.57917</v>
+        <v>16.78731</v>
       </c>
       <c r="F46" t="n">
-        <v>21.69149</v>
+        <v>21.35407</v>
       </c>
       <c r="G46" t="n">
-        <v>35.52769</v>
+        <v>34.72202</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.76378</v>
+        <v>17.09379</v>
       </c>
       <c r="D47" t="n">
-        <v>15.86643</v>
+        <v>16.06068</v>
       </c>
       <c r="E47" t="n">
-        <v>16.63515</v>
+        <v>16.4276</v>
       </c>
       <c r="F47" t="n">
-        <v>21.99947</v>
+        <v>21.89702</v>
       </c>
       <c r="G47" t="n">
-        <v>33.97562</v>
+        <v>35.263</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Unit 10</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.95222</v>
+        <v>17.04022</v>
       </c>
       <c r="D48" t="n">
-        <v>16.10917</v>
+        <v>16.04016</v>
       </c>
       <c r="E48" t="n">
-        <v>16.54941</v>
+        <v>16.62157</v>
       </c>
       <c r="F48" t="n">
-        <v>21.38752</v>
+        <v>21.8222</v>
       </c>
       <c r="G48" t="n">
-        <v>34.80237</v>
+        <v>34.44663</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Unit 11</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.81003</v>
+        <v>16.79149</v>
       </c>
       <c r="D49" t="n">
-        <v>16.19759</v>
+        <v>15.90347</v>
       </c>
       <c r="E49" t="n">
-        <v>16.5363</v>
+        <v>16.60506</v>
       </c>
       <c r="F49" t="n">
-        <v>21.57737</v>
+        <v>22.14864</v>
       </c>
       <c r="G49" t="n">
-        <v>34.78419</v>
+        <v>34.25259</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Unit 12</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>17.05598</v>
+        <v>16.50609</v>
       </c>
       <c r="D50" t="n">
-        <v>15.87211</v>
+        <v>16.20075</v>
       </c>
       <c r="E50" t="n">
-        <v>16.81089</v>
+        <v>16.36724</v>
       </c>
       <c r="F50" t="n">
-        <v>21.79194</v>
+        <v>21.76493</v>
       </c>
       <c r="G50" t="n">
-        <v>34.24511</v>
+        <v>34.18098</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Unit 13</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>16.89491</v>
-      </c>
-      <c r="D51" t="n">
-        <v>16.33182</v>
-      </c>
-      <c r="E51" t="n">
-        <v>16.52365</v>
-      </c>
-      <c r="F51" t="n">
-        <v>22.45068</v>
-      </c>
-      <c r="G51" t="n">
-        <v>34.6023</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Unit 14</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>16.90641</v>
+        <v>0.61448</v>
       </c>
       <c r="D52" t="n">
-        <v>16.14128</v>
-      </c>
-      <c r="E52" t="n">
-        <v>16.6353</v>
-      </c>
-      <c r="F52" t="n">
-        <v>22.05822</v>
-      </c>
-      <c r="G52" t="n">
-        <v>34.50725</v>
+        <v>1.12735</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Unit 15</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17.10046</v>
+        <v>0.61276</v>
       </c>
       <c r="D53" t="n">
-        <v>15.99399</v>
-      </c>
-      <c r="E53" t="n">
-        <v>16.44316</v>
-      </c>
-      <c r="F53" t="n">
-        <v>21.87863</v>
-      </c>
-      <c r="G53" t="n">
-        <v>33.80615</v>
+        <v>1.14221</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Unit 16</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>16.73643</v>
+        <v>0.60136</v>
       </c>
       <c r="D54" t="n">
-        <v>16.14984</v>
-      </c>
-      <c r="E54" t="n">
-        <v>16.61218</v>
-      </c>
-      <c r="F54" t="n">
-        <v>21.92048</v>
-      </c>
-      <c r="G54" t="n">
-        <v>34.13324</v>
+        <v>1.12915</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Unit 17</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>16.56733</v>
+        <v>0.61175</v>
       </c>
       <c r="D55" t="n">
-        <v>16.13918</v>
-      </c>
-      <c r="E55" t="n">
-        <v>16.63243</v>
-      </c>
-      <c r="F55" t="n">
-        <v>22.06885</v>
-      </c>
-      <c r="G55" t="n">
-        <v>34.22606</v>
+        <v>1.14601</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Unit 18</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>17.08273</v>
+        <v>0.6159</v>
       </c>
       <c r="D56" t="n">
-        <v>16.13945</v>
-      </c>
-      <c r="E56" t="n">
-        <v>16.23498</v>
-      </c>
-      <c r="F56" t="n">
-        <v>21.78068</v>
-      </c>
-      <c r="G56" t="n">
-        <v>34.74216</v>
+        <v>1.09613</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Unit 19</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>16.95248</v>
+        <v>0.60486</v>
       </c>
       <c r="D57" t="n">
-        <v>15.75492</v>
-      </c>
-      <c r="E57" t="n">
-        <v>16.74953</v>
-      </c>
-      <c r="F57" t="n">
-        <v>21.7548</v>
-      </c>
-      <c r="G57" t="n">
-        <v>34.9189</v>
+        <v>1.1114</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Unit 20</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>16.95267</v>
+        <v>0.60697</v>
       </c>
       <c r="D58" t="n">
-        <v>16.29985</v>
-      </c>
-      <c r="E58" t="n">
-        <v>16.45663</v>
-      </c>
-      <c r="F58" t="n">
-        <v>22.35371</v>
-      </c>
-      <c r="G58" t="n">
-        <v>34.23493</v>
+        <v>1.12551</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Unit 21</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>17.07075</v>
+        <v>0.6041800000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>16.28421</v>
-      </c>
-      <c r="E59" t="n">
-        <v>16.66626</v>
-      </c>
-      <c r="F59" t="n">
-        <v>22.27443</v>
-      </c>
-      <c r="G59" t="n">
-        <v>34.62102</v>
+        <v>1.12968</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Unit 22</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>16.64648</v>
+        <v>0.60517</v>
       </c>
       <c r="D60" t="n">
-        <v>15.97105</v>
-      </c>
-      <c r="E60" t="n">
-        <v>16.22842</v>
-      </c>
-      <c r="F60" t="n">
-        <v>21.99457</v>
-      </c>
-      <c r="G60" t="n">
-        <v>33.66445</v>
+        <v>1.1045</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Unit 23</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>16.90502</v>
-      </c>
-      <c r="D61" t="n">
-        <v>15.84577</v>
-      </c>
-      <c r="E61" t="n">
-        <v>16.74909</v>
-      </c>
-      <c r="F61" t="n">
-        <v>21.86678</v>
-      </c>
-      <c r="G61" t="n">
-        <v>34.59168</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Unit 24</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>16.90569</v>
+        <v>0.60919</v>
       </c>
       <c r="D62" t="n">
-        <v>15.95518</v>
-      </c>
-      <c r="E62" t="n">
-        <v>16.43755</v>
-      </c>
-      <c r="F62" t="n">
-        <v>21.67802</v>
-      </c>
-      <c r="G62" t="n">
-        <v>34.49921</v>
+        <v>1.11973</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Unit 25</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>16.80966</v>
+        <v>0.61245</v>
       </c>
       <c r="D63" t="n">
-        <v>16.26171</v>
-      </c>
-      <c r="E63" t="n">
-        <v>16.65857</v>
-      </c>
-      <c r="F63" t="n">
-        <v>21.91195</v>
-      </c>
-      <c r="G63" t="n">
-        <v>34.8823</v>
+        <v>1.12665</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Unit 26</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>16.6895</v>
+        <v>0.60604</v>
       </c>
       <c r="D64" t="n">
-        <v>16.36398</v>
-      </c>
-      <c r="E64" t="n">
-        <v>16.28669</v>
-      </c>
-      <c r="F64" t="n">
-        <v>21.44056</v>
-      </c>
-      <c r="G64" t="n">
-        <v>34.11648</v>
+        <v>1.10959</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Unit 27</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>16.59292</v>
+        <v>0.61154</v>
       </c>
       <c r="D65" t="n">
-        <v>16.11686</v>
-      </c>
-      <c r="E65" t="n">
-        <v>16.57997</v>
-      </c>
-      <c r="F65" t="n">
-        <v>22.13534</v>
-      </c>
-      <c r="G65" t="n">
-        <v>34.29296</v>
+        <v>1.13721</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Unit 28</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>17.07529</v>
+        <v>0.60908</v>
       </c>
       <c r="D66" t="n">
-        <v>15.85161</v>
-      </c>
-      <c r="E66" t="n">
-        <v>16.62271</v>
-      </c>
-      <c r="F66" t="n">
-        <v>21.85946</v>
-      </c>
-      <c r="G66" t="n">
-        <v>34.46712</v>
+        <v>1.09974</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Unit 29</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>16.60538</v>
+        <v>0.59785</v>
       </c>
       <c r="D67" t="n">
-        <v>15.76306</v>
-      </c>
-      <c r="E67" t="n">
-        <v>16.1959</v>
-      </c>
-      <c r="F67" t="n">
-        <v>21.74226</v>
-      </c>
-      <c r="G67" t="n">
-        <v>34.13783</v>
+        <v>1.11503</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Unit 30</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>16.63216</v>
+        <v>0.60983</v>
       </c>
       <c r="D68" t="n">
-        <v>16.07512</v>
-      </c>
-      <c r="E68" t="n">
-        <v>16.19563</v>
-      </c>
-      <c r="F68" t="n">
-        <v>22.30083</v>
-      </c>
-      <c r="G68" t="n">
-        <v>33.57058</v>
+        <v>1.13703</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Unit 31</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>16.9501</v>
+        <v>0.61203</v>
       </c>
       <c r="D69" t="n">
-        <v>16.3686</v>
-      </c>
-      <c r="E69" t="n">
-        <v>16.46728</v>
-      </c>
-      <c r="F69" t="n">
-        <v>21.80207</v>
-      </c>
-      <c r="G69" t="n">
-        <v>34.42415</v>
+        <v>1.12829</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Unit 32</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>17.21419</v>
+        <v>0.61217</v>
       </c>
       <c r="D70" t="n">
-        <v>16.3173</v>
-      </c>
-      <c r="E70" t="n">
-        <v>16.44624</v>
-      </c>
-      <c r="F70" t="n">
-        <v>22.0595</v>
-      </c>
-      <c r="G70" t="n">
-        <v>34.30654</v>
+        <v>1.11984</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Unit 33</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>16.81566</v>
-      </c>
-      <c r="D71" t="n">
-        <v>15.9006</v>
-      </c>
-      <c r="E71" t="n">
-        <v>16.30609</v>
-      </c>
-      <c r="F71" t="n">
-        <v>22.285</v>
-      </c>
-      <c r="G71" t="n">
-        <v>34.81973</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Unit 34</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>16.72094</v>
+        <v>0.75457</v>
       </c>
       <c r="D72" t="n">
-        <v>15.80583</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>16.6109</v>
+        <v>0.60286</v>
       </c>
       <c r="F72" t="n">
-        <v>21.72195</v>
+        <v>0.96737</v>
       </c>
       <c r="G72" t="n">
-        <v>34.21649</v>
+        <v>0.10954</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09525</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12745</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Unit 35</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>16.68598</v>
+        <v>0.74586</v>
       </c>
       <c r="D73" t="n">
-        <v>16.18127</v>
+        <v>0.08167000000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>16.60278</v>
+        <v>0.62261</v>
       </c>
       <c r="F73" t="n">
-        <v>21.95717</v>
+        <v>0.9482</v>
       </c>
       <c r="G73" t="n">
-        <v>35.09703</v>
+        <v>0.11182</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09247</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12802</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Unit 36</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>16.53736</v>
+        <v>0.7498</v>
       </c>
       <c r="D74" t="n">
-        <v>16.21876</v>
+        <v>0.08019</v>
       </c>
       <c r="E74" t="n">
-        <v>16.5173</v>
+        <v>0.61358</v>
       </c>
       <c r="F74" t="n">
-        <v>22.3993</v>
+        <v>0.9617</v>
       </c>
       <c r="G74" t="n">
-        <v>34.69591</v>
+        <v>0.10794</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09177</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12734</v>
       </c>
     </row>
     <row r="75">
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.77346</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08228000000000001</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.61851</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.96085</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09236999999999999</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12856</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.75135</v>
       </c>
       <c r="D76" t="n">
-        <v>0.08065</v>
+        <v>0.08013000000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>0.60622</v>
+        <v>0.59721</v>
       </c>
       <c r="F76" t="n">
-        <v>0.96104</v>
+        <v>0.98145</v>
       </c>
       <c r="G76" t="n">
-        <v>0.1105</v>
+        <v>0.1085</v>
       </c>
       <c r="H76" t="n">
-        <v>0.00755</v>
+        <v>0.00772</v>
       </c>
       <c r="I76" t="n">
-        <v>0.09447999999999999</v>
+        <v>0.09446</v>
       </c>
       <c r="J76" t="n">
-        <v>0.12608</v>
+        <v>0.12802</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.74303</v>
+        <v>0.74891</v>
       </c>
       <c r="D77" t="n">
-        <v>0.08122</v>
+        <v>0.08194</v>
       </c>
       <c r="E77" t="n">
-        <v>0.61076</v>
+        <v>0.6067900000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>0.96972</v>
+        <v>0.97524</v>
       </c>
       <c r="G77" t="n">
-        <v>0.11062</v>
+        <v>0.11226</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00758</v>
+        <v>0.0077</v>
       </c>
       <c r="I77" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.09404999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1274</v>
+        <v>0.1276</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.76503</v>
+        <v>0.76078</v>
       </c>
       <c r="D78" t="n">
-        <v>0.08121</v>
+        <v>0.08207</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5998599999999999</v>
+        <v>0.60803</v>
       </c>
       <c r="F78" t="n">
-        <v>0.9466</v>
+        <v>0.96855</v>
       </c>
       <c r="G78" t="n">
-        <v>0.10948</v>
+        <v>0.11144</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00762</v>
+        <v>0.00787</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0951</v>
+        <v>0.09209000000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>0.12751</v>
+        <v>0.12504</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.75903</v>
+        <v>0.76028</v>
       </c>
       <c r="D79" t="n">
-        <v>0.08162</v>
+        <v>0.08104</v>
       </c>
       <c r="E79" t="n">
-        <v>0.61082</v>
+        <v>0.61382</v>
       </c>
       <c r="F79" t="n">
-        <v>0.9687</v>
+        <v>0.96307</v>
       </c>
       <c r="G79" t="n">
-        <v>0.10961</v>
+        <v>0.11175</v>
       </c>
       <c r="H79" t="n">
-        <v>0.00754</v>
+        <v>0.00765</v>
       </c>
       <c r="I79" t="n">
-        <v>0.09368</v>
+        <v>0.09384000000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>0.12678</v>
+        <v>0.12946</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.7394500000000001</v>
+        <v>0.75983</v>
       </c>
       <c r="D80" t="n">
-        <v>0.08282</v>
+        <v>0.08189</v>
       </c>
       <c r="E80" t="n">
-        <v>0.61174</v>
+        <v>0.6049</v>
       </c>
       <c r="F80" t="n">
-        <v>0.95752</v>
+        <v>0.95064</v>
       </c>
       <c r="G80" t="n">
-        <v>0.11025</v>
+        <v>0.10721</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00778</v>
+        <v>0.00773</v>
       </c>
       <c r="I80" t="n">
-        <v>0.09182999999999999</v>
+        <v>0.09401</v>
       </c>
       <c r="J80" t="n">
-        <v>0.12942</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>0.76018</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0.08041</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.61448</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.96257</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0.10826</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.09313</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0.12493</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>0.75474</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0.0798</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0.61122</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0.99295</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0.11108</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.09304999999999999</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0.12581</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>0.75268</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0.08032</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0.6171</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.96457</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0.10818</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.00747</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.09505</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0.12558</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>0.76214</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0.08214</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0.61451</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.96143</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0.11062</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.09444</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0.12993</v>
+        <v>0.12973</v>
       </c>
     </row>
   </sheetData>
